--- a/output/tablas/numero_plataformas.xlsx
+++ b/output/tablas/numero_plataformas.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -393,16 +393,16 @@
         <v>43862</v>
       </c>
       <c r="B2">
-        <v>89478.24962070333</v>
+        <v>88491.07134588645</v>
       </c>
       <c r="C2">
-        <v>48248.97063633589</v>
+        <v>48236.60933100921</v>
       </c>
       <c r="D2">
-        <v>8269.404375679025</v>
+        <v>7536.406591739306</v>
       </c>
       <c r="E2">
-        <v>56518.37501201492</v>
+        <v>55773.01592274852</v>
       </c>
     </row>
     <row r="3">
@@ -410,16 +410,16 @@
         <v>43891</v>
       </c>
       <c r="B3">
-        <v>70074.79929177067</v>
+        <v>68640.00016459686</v>
       </c>
       <c r="C3">
-        <v>38002.08078846079</v>
+        <v>38108.81058476942</v>
       </c>
       <c r="D3">
-        <v>7201.695570227678</v>
+        <v>7201.695570227679</v>
       </c>
       <c r="E3">
-        <v>45203.77635868847</v>
+        <v>45310.5061549971</v>
       </c>
     </row>
     <row r="4">
@@ -427,16 +427,16 @@
         <v>43922</v>
       </c>
       <c r="B4">
-        <v>50490.15988147155</v>
+        <v>47843.97463993884</v>
       </c>
       <c r="C4">
-        <v>32888.70128309807</v>
+        <v>30606.92704213435</v>
       </c>
       <c r="D4">
         <v>3723.824119850708</v>
       </c>
       <c r="E4">
-        <v>36612.52540294878</v>
+        <v>34330.75116198506</v>
       </c>
     </row>
     <row r="5">
@@ -444,16 +444,16 @@
         <v>43952</v>
       </c>
       <c r="B5">
-        <v>38671.2370508652</v>
+        <v>36777.22027504075</v>
       </c>
       <c r="C5">
-        <v>29059.45874244924</v>
+        <v>27117.772757939</v>
       </c>
       <c r="D5">
         <v>2136.204948249944</v>
       </c>
       <c r="E5">
-        <v>31195.66369069918</v>
+        <v>29253.97770618894</v>
       </c>
     </row>
     <row r="6">
@@ -461,16 +461,16 @@
         <v>43983</v>
       </c>
       <c r="B6">
-        <v>64709.1885855588</v>
+        <v>63967.99547972264</v>
       </c>
       <c r="C6">
-        <v>32907.24734615842</v>
+        <v>32971.90326394467</v>
       </c>
       <c r="D6">
         <v>4268.714606716563</v>
       </c>
       <c r="E6">
-        <v>37175.96195287498</v>
+        <v>37240.61787066123</v>
       </c>
     </row>
     <row r="7">
@@ -478,16 +478,16 @@
         <v>44013</v>
       </c>
       <c r="B7">
-        <v>105897.7843048779</v>
+        <v>98117.57881939619</v>
       </c>
       <c r="C7">
-        <v>33766.15290617588</v>
+        <v>32717.66259689889</v>
       </c>
       <c r="D7">
         <v>4091.433653240558</v>
       </c>
       <c r="E7">
-        <v>37857.58655941644</v>
+        <v>36809.09625013945</v>
       </c>
     </row>
     <row r="8">
@@ -495,16 +495,16 @@
         <v>44044</v>
       </c>
       <c r="B8">
-        <v>130695.7056333423</v>
+        <v>121003.9877987853</v>
       </c>
       <c r="C8">
-        <v>33882.38194142659</v>
+        <v>31002.4195427435</v>
       </c>
       <c r="D8">
         <v>4399.545841620967</v>
       </c>
       <c r="E8">
-        <v>38281.92778304755</v>
+        <v>35401.96538436447</v>
       </c>
     </row>
     <row r="9">
@@ -512,16 +512,16 @@
         <v>44075</v>
       </c>
       <c r="B9">
-        <v>127925.289751091</v>
+        <v>117333.7408994764</v>
       </c>
       <c r="C9">
-        <v>28747.23488722967</v>
+        <v>25296.6218879851</v>
       </c>
       <c r="D9">
         <v>4642.909342773706</v>
       </c>
       <c r="E9">
-        <v>33390.14423000338</v>
+        <v>29939.53123075881</v>
       </c>
     </row>
     <row r="10">
@@ -529,16 +529,16 @@
         <v>44105</v>
       </c>
       <c r="B10">
-        <v>117305.638845755</v>
+        <v>107611.6822931157</v>
       </c>
       <c r="C10">
-        <v>34989.60668424596</v>
+        <v>30302.90515041072</v>
       </c>
       <c r="D10">
         <v>5568.562666572299</v>
       </c>
       <c r="E10">
-        <v>40558.16935081827</v>
+        <v>35871.46781698302</v>
       </c>
     </row>
     <row r="11">
@@ -546,16 +546,16 @@
         <v>44136</v>
       </c>
       <c r="B11">
-        <v>110932.7369479657</v>
+        <v>96413.63138565946</v>
       </c>
       <c r="C11">
-        <v>37615.21669787962</v>
+        <v>34190.41889262162</v>
       </c>
       <c r="D11">
         <v>5352.568434288097</v>
       </c>
       <c r="E11">
-        <v>42967.78513216772</v>
+        <v>39542.98732690972</v>
       </c>
     </row>
     <row r="12">
@@ -563,16 +563,16 @@
         <v>44166</v>
       </c>
       <c r="B12">
-        <v>111032.700617995</v>
+        <v>96111.92199550517</v>
       </c>
       <c r="C12">
-        <v>39892.5542256327</v>
+        <v>37112.86699439934</v>
       </c>
       <c r="D12">
-        <v>2285.683624272255</v>
+        <v>2285.683624272256</v>
       </c>
       <c r="E12">
-        <v>42178.23784990496</v>
+        <v>39398.55061867159</v>
       </c>
     </row>
     <row r="13">
@@ -580,16 +580,16 @@
         <v>44197</v>
       </c>
       <c r="B13">
-        <v>120950.3458630192</v>
+        <v>106606.9751684796</v>
       </c>
       <c r="C13">
-        <v>43314.11491672425</v>
+        <v>42544.72136155581</v>
       </c>
       <c r="D13">
         <v>3671.123938476724</v>
       </c>
       <c r="E13">
-        <v>46985.23885520098</v>
+        <v>46215.84530003254</v>
       </c>
     </row>
     <row r="14">
@@ -597,16 +597,16 @@
         <v>44228</v>
       </c>
       <c r="B14">
-        <v>125607.6019295157</v>
+        <v>119066.5804558667</v>
       </c>
       <c r="C14">
-        <v>47152.02397312065</v>
+        <v>49547.71912879978</v>
       </c>
       <c r="D14">
         <v>3255.707175699304</v>
       </c>
       <c r="E14">
-        <v>50407.73114881996</v>
+        <v>52803.42630449908</v>
       </c>
     </row>
     <row r="15">
@@ -614,16 +614,16 @@
         <v>44256</v>
       </c>
       <c r="B15">
-        <v>142423.0307056002</v>
+        <v>137069.5837659288</v>
       </c>
       <c r="C15">
-        <v>53462.8872226968</v>
+        <v>55306.5633051851</v>
       </c>
       <c r="D15">
         <v>3263.062490268817</v>
       </c>
       <c r="E15">
-        <v>56725.94971296562</v>
+        <v>58569.62579545392</v>
       </c>
     </row>
     <row r="16">
@@ -631,16 +631,16 @@
         <v>44287</v>
       </c>
       <c r="B16">
-        <v>144112.9716662937</v>
+        <v>139921.3563170253</v>
       </c>
       <c r="C16">
-        <v>49335.1653903239</v>
+        <v>52984.99746485791</v>
       </c>
       <c r="D16">
         <v>1663.410540207817</v>
       </c>
       <c r="E16">
-        <v>50998.57593053172</v>
+        <v>54648.40800506573</v>
       </c>
     </row>
     <row r="17">
@@ -648,16 +648,16 @@
         <v>44317</v>
       </c>
       <c r="B17">
-        <v>152882.6981313551</v>
+        <v>143225.3277803313</v>
       </c>
       <c r="C17">
-        <v>48372.50164612812</v>
+        <v>48363.63447281568</v>
       </c>
       <c r="D17">
         <v>2106.230810167313</v>
       </c>
       <c r="E17">
-        <v>50478.73245629543</v>
+        <v>50469.865282983</v>
       </c>
     </row>
     <row r="18">
@@ -665,16 +665,16 @@
         <v>44348</v>
       </c>
       <c r="B18">
-        <v>148625.1551123548</v>
+        <v>137790.9541693127</v>
       </c>
       <c r="C18">
-        <v>52242.78401103704</v>
+        <v>52177.86671649782</v>
       </c>
       <c r="D18">
-        <v>789.1309425255388</v>
+        <v>1130.800971739731</v>
       </c>
       <c r="E18">
-        <v>53031.91495356258</v>
+        <v>53308.66768823755</v>
       </c>
     </row>
     <row r="19">
@@ -682,16 +682,16 @@
         <v>44378</v>
       </c>
       <c r="B19">
-        <v>168759.8195288064</v>
+        <v>155183.9950436768</v>
       </c>
       <c r="C19">
-        <v>53958.42594541545</v>
+        <v>52922.12264192112</v>
       </c>
       <c r="D19">
-        <v>419.3850094908116</v>
+        <v>757.1418054502917</v>
       </c>
       <c r="E19">
-        <v>54377.81095490626</v>
+        <v>53679.26444737142</v>
       </c>
     </row>
     <row r="20">
@@ -699,16 +699,16 @@
         <v>44409</v>
       </c>
       <c r="B20">
-        <v>174481.4051015412</v>
+        <v>159267.4980792284</v>
       </c>
       <c r="C20">
-        <v>50426.14113387233</v>
+        <v>49199.23509635944</v>
       </c>
       <c r="D20">
-        <v>963.8188472520424</v>
+        <v>839.8094214674074</v>
       </c>
       <c r="E20">
-        <v>51389.95998112437</v>
+        <v>50039.04451782684</v>
       </c>
     </row>
     <row r="21">
@@ -716,16 +716,16 @@
         <v>44440</v>
       </c>
       <c r="B21">
-        <v>180398.7161974137</v>
+        <v>165045.2938010738</v>
       </c>
       <c r="C21">
-        <v>45060.8197622783</v>
+        <v>43461.54117341115</v>
       </c>
       <c r="D21">
-        <v>2484.682818713637</v>
+        <v>1958.057217865614</v>
       </c>
       <c r="E21">
-        <v>47545.50258099193</v>
+        <v>45419.59839127676</v>
       </c>
     </row>
     <row r="22">
@@ -733,16 +733,16 @@
         <v>44470</v>
       </c>
       <c r="B22">
-        <v>171798.1135976381</v>
+        <v>156463.8772866386</v>
       </c>
       <c r="C22">
-        <v>47910.45023523178</v>
+        <v>42357.6783487307</v>
       </c>
       <c r="D22">
-        <v>2647.843615957</v>
+        <v>2073.079289359804</v>
       </c>
       <c r="E22">
-        <v>50558.29385118878</v>
+        <v>44430.75763809051</v>
       </c>
     </row>
     <row r="23">
@@ -750,16 +750,16 @@
         <v>44501</v>
       </c>
       <c r="B23">
-        <v>176859.8714569376</v>
+        <v>163112.0715774382</v>
       </c>
       <c r="C23">
-        <v>54847.28831834491</v>
+        <v>49707.80269195925</v>
       </c>
       <c r="D23">
         <v>2817.016539066142</v>
       </c>
       <c r="E23">
-        <v>57664.30485741105</v>
+        <v>52524.81923102539</v>
       </c>
     </row>
     <row r="24">
@@ -767,16 +767,16 @@
         <v>44531</v>
       </c>
       <c r="B24">
-        <v>185319.3843728361</v>
+        <v>170078.933167208</v>
       </c>
       <c r="C24">
-        <v>60088.85629964725</v>
+        <v>56488.68533184688</v>
       </c>
       <c r="D24">
         <v>6102.922093869061</v>
       </c>
       <c r="E24">
-        <v>66191.77839351632</v>
+        <v>62591.60742571594</v>
       </c>
     </row>
     <row r="25">
@@ -784,16 +784,16 @@
         <v>44562</v>
       </c>
       <c r="B25">
-        <v>180733.6994503199</v>
+        <v>169701.0943680634</v>
       </c>
       <c r="C25">
-        <v>58224.57225460523</v>
+        <v>59571.37394870307</v>
       </c>
       <c r="D25">
-        <v>8341.293917244338</v>
+        <v>8341.293917244337</v>
       </c>
       <c r="E25">
-        <v>66565.86617184957</v>
+        <v>67912.66786594741</v>
       </c>
     </row>
     <row r="26">
@@ -801,16 +801,16 @@
         <v>44593</v>
       </c>
       <c r="B26">
-        <v>178652.6451986936</v>
+        <v>166518.3951069183</v>
       </c>
       <c r="C26">
-        <v>56321.632640249</v>
+        <v>58092.493607593</v>
       </c>
       <c r="D26">
         <v>7711.050951108623</v>
       </c>
       <c r="E26">
-        <v>64032.68359135762</v>
+        <v>65803.54455870163</v>
       </c>
     </row>
     <row r="27">
@@ -818,16 +818,16 @@
         <v>44621</v>
       </c>
       <c r="B27">
-        <v>173174.8881891246</v>
+        <v>164054.9645784177</v>
       </c>
       <c r="C27">
-        <v>54995.40025754338</v>
+        <v>55694.82736005987</v>
       </c>
       <c r="D27">
         <v>6653.598665400261</v>
       </c>
       <c r="E27">
-        <v>61648.99892294365</v>
+        <v>62348.42602546013</v>
       </c>
     </row>
     <row r="28">
@@ -835,16 +835,16 @@
         <v>44652</v>
       </c>
       <c r="B28">
-        <v>183226.4190832599</v>
+        <v>170330.2331582338</v>
       </c>
       <c r="C28">
-        <v>52161.17552295687</v>
+        <v>51841.8393386224</v>
       </c>
       <c r="D28">
         <v>6196.313964457395</v>
       </c>
       <c r="E28">
-        <v>58357.48948741427</v>
+        <v>58038.15330307979</v>
       </c>
     </row>
     <row r="29">
@@ -852,16 +852,16 @@
         <v>44682</v>
       </c>
       <c r="B29">
-        <v>181805.0041309627</v>
+        <v>170203.2631328624</v>
       </c>
       <c r="C29">
-        <v>50071.01877674028</v>
+        <v>48996.36708013636</v>
       </c>
       <c r="D29">
         <v>6767.273823917919</v>
       </c>
       <c r="E29">
-        <v>56838.2926006582</v>
+        <v>55763.64090405427</v>
       </c>
     </row>
     <row r="30">
@@ -869,16 +869,16 @@
         <v>44713</v>
       </c>
       <c r="B30">
-        <v>193571.4367346837</v>
+        <v>181175.4638377262</v>
       </c>
       <c r="C30">
-        <v>46413.2005778297</v>
+        <v>47889.56826785448</v>
       </c>
       <c r="D30">
         <v>5106.660151242744</v>
       </c>
       <c r="E30">
-        <v>51519.86072907244</v>
+        <v>52996.22841909723</v>
       </c>
     </row>
     <row r="31">
@@ -886,16 +886,16 @@
         <v>44743</v>
       </c>
       <c r="B31">
-        <v>189200.1915607535</v>
+        <v>178994.8092888517</v>
       </c>
       <c r="C31">
-        <v>39881.31408848692</v>
+        <v>41452.26864146012</v>
       </c>
       <c r="D31">
         <v>2866.325421198601</v>
       </c>
       <c r="E31">
-        <v>42747.63950968552</v>
+        <v>44318.59406265872</v>
       </c>
     </row>
     <row r="32">
@@ -903,16 +903,16 @@
         <v>44774</v>
       </c>
       <c r="B32">
-        <v>199987.4041560638</v>
+        <v>185886.962553806</v>
       </c>
       <c r="C32">
-        <v>44526.45048479899</v>
+        <v>47215.21919578069</v>
       </c>
       <c r="D32">
         <v>2631.790286798008</v>
       </c>
       <c r="E32">
-        <v>47158.240771597</v>
+        <v>49847.00948257869</v>
       </c>
     </row>
     <row r="33">
@@ -920,16 +920,16 @@
         <v>44805</v>
       </c>
       <c r="B33">
-        <v>192390.6778946531</v>
+        <v>175508.6553310996</v>
       </c>
       <c r="C33">
-        <v>43873.81974687832</v>
+        <v>45046.53555642023</v>
       </c>
       <c r="D33">
         <v>1583.593719970836</v>
       </c>
       <c r="E33">
-        <v>45457.41346684915</v>
+        <v>46630.12927639107</v>
       </c>
     </row>
     <row r="34">
@@ -937,16 +937,16 @@
         <v>44835</v>
       </c>
       <c r="B34">
-        <v>194900.140977795</v>
+        <v>174522.9304439457</v>
       </c>
       <c r="C34">
-        <v>49086.86892781863</v>
+        <v>50201.93024198765</v>
       </c>
       <c r="D34">
         <v>3349.434482590654</v>
       </c>
       <c r="E34">
-        <v>52436.30341040928</v>
+        <v>53551.3647245783</v>
       </c>
     </row>
     <row r="35">
@@ -954,16 +954,16 @@
         <v>44866</v>
       </c>
       <c r="B35">
-        <v>195907.2891898076</v>
+        <v>181505.8945205147</v>
       </c>
       <c r="C35">
-        <v>52273.28418513335</v>
+        <v>52496.62764393002</v>
       </c>
       <c r="D35">
         <v>4202.45601309321</v>
       </c>
       <c r="E35">
-        <v>56475.74019822656</v>
+        <v>56699.08365702323</v>
       </c>
     </row>
     <row r="36">
@@ -971,16 +971,16 @@
         <v>44896</v>
       </c>
       <c r="B36">
-        <v>198146.214491672</v>
+        <v>184548.4119496523</v>
       </c>
       <c r="C36">
-        <v>53510.70020392885</v>
+        <v>55143.16224976148</v>
       </c>
       <c r="D36">
         <v>4972.711799544366</v>
       </c>
       <c r="E36">
-        <v>58483.41200347322</v>
+        <v>60115.87404930584</v>
       </c>
     </row>
     <row r="37">
@@ -988,16 +988,16 @@
         <v>44927</v>
       </c>
       <c r="B37">
-        <v>198531.1396000765</v>
+        <v>188262.5668955287</v>
       </c>
       <c r="C37">
-        <v>47848.09006731727</v>
+        <v>51349.00364557674</v>
       </c>
       <c r="D37">
         <v>4367.302102299227</v>
       </c>
       <c r="E37">
-        <v>52215.3921696165</v>
+        <v>55716.30574787597</v>
       </c>
     </row>
     <row r="38">
@@ -1005,16 +1005,16 @@
         <v>44958</v>
       </c>
       <c r="B38">
-        <v>200787.4821557744</v>
+        <v>187471.7140803387</v>
       </c>
       <c r="C38">
-        <v>44389.05561176606</v>
+        <v>48476.45394374705</v>
       </c>
       <c r="D38">
         <v>3526.826953334525</v>
       </c>
       <c r="E38">
-        <v>47915.88256510058</v>
+        <v>52003.28089708157</v>
       </c>
     </row>
     <row r="39">
@@ -1022,16 +1022,16 @@
         <v>44986</v>
       </c>
       <c r="B39">
-        <v>215615.7739542554</v>
+        <v>197811.7489779338</v>
       </c>
       <c r="C39">
-        <v>47418.61658008629</v>
+        <v>48776.84671027958</v>
       </c>
       <c r="D39">
-        <v>5178.424714877468</v>
+        <v>5178.424714877467</v>
       </c>
       <c r="E39">
-        <v>52597.04129496376</v>
+        <v>53955.27142515705</v>
       </c>
     </row>
     <row r="40">
@@ -1039,16 +1039,16 @@
         <v>45017</v>
       </c>
       <c r="B40">
-        <v>212262.358742589</v>
+        <v>194848.8626614226</v>
       </c>
       <c r="C40">
-        <v>48088.46602213665</v>
+        <v>47659.45096248807</v>
       </c>
       <c r="D40">
         <v>5113.515237576241</v>
       </c>
       <c r="E40">
-        <v>53201.98125971289</v>
+        <v>52772.96620006431</v>
       </c>
     </row>
     <row r="41">
@@ -1056,16 +1056,16 @@
         <v>45047</v>
       </c>
       <c r="B41">
-        <v>229885.1595417914</v>
+        <v>214175.7260359662</v>
       </c>
       <c r="C41">
-        <v>55818.70138042347</v>
+        <v>56148.85510009451</v>
       </c>
       <c r="D41">
-        <v>5289.941432565874</v>
+        <v>5491.023494019693</v>
       </c>
       <c r="E41">
-        <v>61108.64281298934</v>
+        <v>61639.8785941142</v>
       </c>
     </row>
     <row r="42">
@@ -1073,16 +1073,16 @@
         <v>45078</v>
       </c>
       <c r="B42">
-        <v>235610.0305967931</v>
+        <v>220672.0385710547</v>
       </c>
       <c r="C42">
-        <v>54978.17446063594</v>
+        <v>56175.85054731127</v>
       </c>
       <c r="D42">
-        <v>4360.450424134761</v>
+        <v>4563.115995469119</v>
       </c>
       <c r="E42">
-        <v>59338.6248847707</v>
+        <v>60738.96654278038</v>
       </c>
     </row>
     <row r="43">
@@ -1090,16 +1090,16 @@
         <v>45108</v>
       </c>
       <c r="B43">
-        <v>256211.6457550502</v>
+        <v>237818.1495112421</v>
       </c>
       <c r="C43">
-        <v>61582.64403831042</v>
+        <v>62014.48555750465</v>
       </c>
       <c r="D43">
-        <v>6147.247666668534</v>
+        <v>6570.083893058252</v>
       </c>
       <c r="E43">
-        <v>67729.89170497896</v>
+        <v>68584.56945056291</v>
       </c>
     </row>
     <row r="44">
@@ -1107,16 +1107,16 @@
         <v>45139</v>
       </c>
       <c r="B44">
-        <v>267763.1937798181</v>
+        <v>248676.8638880833</v>
       </c>
       <c r="C44">
-        <v>59003.53101027941</v>
+        <v>59673.31606542262</v>
       </c>
       <c r="D44">
-        <v>6532.009099910201</v>
+        <v>6739.995184589316</v>
       </c>
       <c r="E44">
-        <v>65535.54011018961</v>
+        <v>66413.31125001193</v>
       </c>
     </row>
     <row r="45">
@@ -1124,16 +1124,16 @@
         <v>45170</v>
       </c>
       <c r="B45">
-        <v>254465.6656515858</v>
+        <v>236625.1771884882</v>
       </c>
       <c r="C45">
-        <v>60712.92603170737</v>
+        <v>60987.8746948617</v>
       </c>
       <c r="D45">
-        <v>5977.675232275271</v>
+        <v>6186.332573723052</v>
       </c>
       <c r="E45">
-        <v>66690.60126398264</v>
+        <v>67174.20726858475</v>
       </c>
     </row>
     <row r="46">
@@ -1141,16 +1141,16 @@
         <v>45200</v>
       </c>
       <c r="B46">
-        <v>249231.327724594</v>
+        <v>233874.361272312</v>
       </c>
       <c r="C46">
-        <v>66834.41472408062</v>
+        <v>67559.20649534222</v>
       </c>
       <c r="D46">
         <v>5197.757575839634</v>
       </c>
       <c r="E46">
-        <v>72032.17229992026</v>
+        <v>72756.96407118186</v>
       </c>
     </row>
     <row r="47">
@@ -1158,16 +1158,16 @@
         <v>45231</v>
       </c>
       <c r="B47">
-        <v>226798.0692415599</v>
+        <v>210444.5394789354</v>
       </c>
       <c r="C47">
-        <v>67932.58164806566</v>
+        <v>66357.55189162487</v>
       </c>
       <c r="D47">
-        <v>5050.890909897597</v>
+        <v>5309.836827753625</v>
       </c>
       <c r="E47">
-        <v>72983.47255796326</v>
+        <v>71667.38871937849</v>
       </c>
     </row>
     <row r="48">
@@ -1175,16 +1175,16 @@
         <v>45261</v>
       </c>
       <c r="B48">
-        <v>242875.0468277518</v>
+        <v>229163.347670668</v>
       </c>
       <c r="C48">
-        <v>69399.19940771555</v>
+        <v>67877.88496310019</v>
       </c>
       <c r="D48">
-        <v>5532.638383789267</v>
+        <v>5788.424277837339</v>
       </c>
       <c r="E48">
-        <v>74931.83779150482</v>
+        <v>73666.30924093754</v>
       </c>
     </row>
     <row r="49">
@@ -1192,16 +1192,16 @@
         <v>45292</v>
       </c>
       <c r="B49">
-        <v>241230.5171586379</v>
+        <v>227788.851683885</v>
       </c>
       <c r="C49">
-        <v>65382.0359085455</v>
+        <v>62417.07410282281</v>
       </c>
       <c r="D49">
-        <v>8235.817700748452</v>
+        <v>8499.102153954527</v>
       </c>
       <c r="E49">
-        <v>73617.85360929395</v>
+        <v>70916.17625677734</v>
       </c>
     </row>
     <row r="50">
@@ -1209,16 +1209,16 @@
         <v>45323</v>
       </c>
       <c r="B50">
-        <v>249505.2640797923</v>
+        <v>236191.9236103065</v>
       </c>
       <c r="C50">
-        <v>74194.7196425289</v>
+        <v>72173.24325970333</v>
       </c>
       <c r="D50">
         <v>8748.592899366555</v>
       </c>
       <c r="E50">
-        <v>82943.31254189546</v>
+        <v>80921.83615906989</v>
       </c>
     </row>
     <row r="51">
@@ -1226,16 +1226,16 @@
         <v>45352</v>
       </c>
       <c r="B51">
-        <v>255036.8116187704</v>
+        <v>241463.6407551908</v>
       </c>
       <c r="C51">
-        <v>77111.70745067032</v>
+        <v>74524.31921502581</v>
       </c>
       <c r="D51">
         <v>10450.5297164524</v>
       </c>
       <c r="E51">
-        <v>87562.23716712272</v>
+        <v>84974.84893147821</v>
       </c>
     </row>
     <row r="52">
@@ -1243,16 +1243,16 @@
         <v>45383</v>
       </c>
       <c r="B52">
-        <v>269107.9459293363</v>
+        <v>254035.5851467194</v>
       </c>
       <c r="C52">
-        <v>73065.99254606733</v>
+        <v>71891.02901163133</v>
       </c>
       <c r="D52">
-        <v>6322.852762931674</v>
+        <v>6239.441920438418</v>
       </c>
       <c r="E52">
-        <v>79388.84530899901</v>
+        <v>78130.47093206974</v>
       </c>
     </row>
     <row r="53">
@@ -1260,16 +1260,16 @@
         <v>45413</v>
       </c>
       <c r="B53">
-        <v>290239.4697429846</v>
+        <v>269609.8680806893</v>
       </c>
       <c r="C53">
-        <v>70954.44748013405</v>
+        <v>65071.87502474294</v>
       </c>
       <c r="D53">
-        <v>5743.332922243399</v>
+        <v>8237.616588007488</v>
       </c>
       <c r="E53">
-        <v>76697.78040237745</v>
+        <v>73309.49161275043</v>
       </c>
     </row>
     <row r="54">
@@ -1277,16 +1277,16 @@
         <v>45444</v>
       </c>
       <c r="B54">
-        <v>302141.8735904631</v>
+        <v>275677.8393703107</v>
       </c>
       <c r="C54">
-        <v>73817.22916946535</v>
+        <v>66687.66343178286</v>
       </c>
       <c r="D54">
-        <v>2423.144278940126</v>
+        <v>4993.247923886036</v>
       </c>
       <c r="E54">
-        <v>76240.37344840547</v>
+        <v>71680.9113556689</v>
       </c>
     </row>
     <row r="55">
@@ -1294,16 +1294,16 @@
         <v>45474</v>
       </c>
       <c r="B55">
-        <v>323973.4988067271</v>
+        <v>295952.3157146077</v>
       </c>
       <c r="C55">
-        <v>83906.18733854414</v>
+        <v>77519.388228764</v>
       </c>
       <c r="D55">
-        <v>3486.87631573579</v>
+        <v>6095.94998986127</v>
       </c>
       <c r="E55">
-        <v>87393.06365427993</v>
+        <v>83615.33821862527</v>
       </c>
     </row>
     <row r="56">
@@ -1311,16 +1311,16 @@
         <v>45505</v>
       </c>
       <c r="B56">
-        <v>313467.4943569872</v>
+        <v>291651.809829718</v>
       </c>
       <c r="C56">
-        <v>78101.81676306389</v>
+        <v>76304.9439655778</v>
       </c>
       <c r="D56">
         <v>4307.43211357628</v>
       </c>
       <c r="E56">
-        <v>82409.24887664017</v>
+        <v>80612.37607915408</v>
       </c>
     </row>
     <row r="57">
@@ -1328,16 +1328,16 @@
         <v>45536</v>
       </c>
       <c r="B57">
-        <v>312882.0111064587</v>
+        <v>291552.859463023</v>
       </c>
       <c r="C57">
-        <v>75789.82852808564</v>
+        <v>75971.56711285215</v>
       </c>
       <c r="D57">
-        <v>5259.718048545043</v>
+        <v>5259.718048545041</v>
       </c>
       <c r="E57">
-        <v>81049.54657663067</v>
+        <v>81231.28516139719</v>
       </c>
     </row>
     <row r="58">
@@ -1345,16 +1345,16 @@
         <v>45566</v>
       </c>
       <c r="B58">
-        <v>298804.6184082197</v>
+        <v>279815.0406334464</v>
       </c>
       <c r="C58">
-        <v>73585.80575013094</v>
+        <v>73875.54870583532</v>
       </c>
       <c r="D58">
-        <v>4583.354361081431</v>
+        <v>4583.35436108143</v>
       </c>
       <c r="E58">
-        <v>78169.16011121238</v>
+        <v>78458.90306691674</v>
       </c>
     </row>
     <row r="59">
@@ -1362,16 +1362,16 @@
         <v>45597</v>
       </c>
       <c r="B59">
-        <v>303369.0312107654</v>
+        <v>284809.0942226198</v>
       </c>
       <c r="C59">
-        <v>82494.3731204605</v>
+        <v>83819.23157833515</v>
       </c>
       <c r="D59">
         <v>5349.014284544735</v>
       </c>
       <c r="E59">
-        <v>87843.38740500524</v>
+        <v>89168.24586287989</v>
       </c>
     </row>
     <row r="60">
@@ -1379,16 +1379,16 @@
         <v>45627</v>
       </c>
       <c r="B60">
-        <v>301611.7327979105</v>
+        <v>286433.9446054431</v>
       </c>
       <c r="C60">
-        <v>84857.05677992055</v>
+        <v>86149.23455652069</v>
       </c>
       <c r="D60">
-        <v>6620.754113483605</v>
+        <v>6620.754113483606</v>
       </c>
       <c r="E60">
-        <v>91477.81089340415</v>
+        <v>92769.9886700043</v>
       </c>
     </row>
     <row r="61">
@@ -1396,16 +1396,16 @@
         <v>45658</v>
       </c>
       <c r="B61">
-        <v>306881.8535005677</v>
+        <v>288519.2224757191</v>
       </c>
       <c r="C61">
-        <v>86570.00518907301</v>
+        <v>88782.14762823179</v>
       </c>
       <c r="D61">
-        <v>7366.955655010516</v>
+        <v>7366.955655010517</v>
       </c>
       <c r="E61">
-        <v>93936.96084408353</v>
+        <v>96149.10328324231</v>
       </c>
     </row>
     <row r="62">
@@ -1413,16 +1413,16 @@
         <v>45689</v>
       </c>
       <c r="B62">
-        <v>301219.4640807723</v>
+        <v>278515.9339674744</v>
       </c>
       <c r="C62">
-        <v>77801.97905129552</v>
+        <v>78734.03363368928</v>
       </c>
       <c r="D62">
         <v>5630.029812667311</v>
       </c>
       <c r="E62">
-        <v>83432.00886396284</v>
+        <v>84364.06344635659</v>
       </c>
     </row>
     <row r="63">
@@ -1430,16 +1430,16 @@
         <v>45717</v>
       </c>
       <c r="B63">
-        <v>298096.2585896627</v>
+        <v>273633.5379272717</v>
       </c>
       <c r="C63">
-        <v>77740.08625171299</v>
+        <v>78816.8086461709</v>
       </c>
       <c r="D63">
-        <v>4033.309453622943</v>
+        <v>4033.309453622942</v>
       </c>
       <c r="E63">
-        <v>81773.39570533593</v>
+        <v>82850.11809979385</v>
       </c>
     </row>
     <row r="64">
@@ -1447,16 +1447,16 @@
         <v>45748</v>
       </c>
       <c r="B64">
-        <v>293550.6685084761</v>
+        <v>274391.10571762</v>
       </c>
       <c r="C64">
-        <v>74364.74433429923</v>
+        <v>76241.78265496698</v>
       </c>
       <c r="D64">
         <v>4939.239633574831</v>
       </c>
       <c r="E64">
-        <v>79303.98396787407</v>
+        <v>81181.02228854182</v>
       </c>
     </row>
     <row r="65">
@@ -1464,16 +1464,16 @@
         <v>45778</v>
       </c>
       <c r="B65">
-        <v>305479.6884967079</v>
+        <v>284523.2871282637</v>
       </c>
       <c r="C65">
-        <v>72651.12852460878</v>
+        <v>74459.27827310647</v>
       </c>
       <c r="D65">
-        <v>7052.541086891</v>
+        <v>7052.541086891001</v>
       </c>
       <c r="E65">
-        <v>79703.66961149978</v>
+        <v>81511.81935999746</v>
       </c>
     </row>
     <row r="66">
@@ -1481,16 +1481,16 @@
         <v>45809</v>
       </c>
       <c r="B66">
-        <v>329337.8458232514</v>
+        <v>307395.1168593073</v>
       </c>
       <c r="C66">
-        <v>78649.94963095353</v>
+        <v>80728.03281018855</v>
       </c>
       <c r="D66">
-        <v>7474.653599245121</v>
+        <v>7474.65359924512</v>
       </c>
       <c r="E66">
-        <v>86124.60323019866</v>
+        <v>88202.68640943368</v>
       </c>
     </row>
     <row r="67">
@@ -1498,16 +1498,16 @@
         <v>45839</v>
       </c>
       <c r="B67">
-        <v>362854.5531291424</v>
+        <v>332535.4759233722</v>
       </c>
       <c r="C67">
-        <v>82330.25441622012</v>
+        <v>81297.1619948232</v>
       </c>
       <c r="D67">
         <v>7832.121592854902</v>
       </c>
       <c r="E67">
-        <v>90162.37600907503</v>
+        <v>89129.2835876781</v>
       </c>
     </row>
     <row r="68">
@@ -1515,16 +1515,16 @@
         <v>45870</v>
       </c>
       <c r="B68">
-        <v>360463.0514293145</v>
+        <v>335826.1275810536</v>
       </c>
       <c r="C68">
-        <v>80225.56295888871</v>
+        <v>80320.8041764456</v>
       </c>
       <c r="D68">
-        <v>7290.535618679247</v>
+        <v>7701.962298331651</v>
       </c>
       <c r="E68">
-        <v>87516.09857756796</v>
+        <v>88022.76647477725</v>
       </c>
     </row>
     <row r="69">
@@ -1532,16 +1532,16 @@
         <v>45901</v>
       </c>
       <c r="B69">
-        <v>349174.5029360235</v>
+        <v>326368.6357175083</v>
       </c>
       <c r="C69">
-        <v>71657.23508635352</v>
+        <v>71718.07303737955</v>
       </c>
       <c r="D69">
-        <v>9582.714823114395</v>
+        <v>9998.895393984905</v>
       </c>
       <c r="E69">
-        <v>81239.94990946792</v>
+        <v>81716.96843136445</v>
       </c>
     </row>
     <row r="70">
@@ -1549,16 +1549,16 @@
         <v>45931</v>
       </c>
       <c r="B70">
-        <v>331481.2047105883</v>
+        <v>312177.1879910644</v>
       </c>
       <c r="C70">
-        <v>63269.35200125635</v>
+        <v>64921.4959795128</v>
       </c>
       <c r="D70">
-        <v>9372.749389508233</v>
+        <v>9776.588288412371</v>
       </c>
       <c r="E70">
-        <v>72642.10139076458</v>
+        <v>74698.08426792518</v>
       </c>
     </row>
     <row r="71">
@@ -1566,16 +1566,16 @@
         <v>45962</v>
       </c>
       <c r="B71">
-        <v>343048.3784682359</v>
+        <v>323499.1400499934</v>
       </c>
       <c r="C71">
-        <v>72461.6147487095</v>
+        <v>74629.21959826576</v>
       </c>
       <c r="D71">
         <v>10204.88093854109</v>
       </c>
       <c r="E71">
-        <v>82666.49568725059</v>
+        <v>84834.10053680684</v>
       </c>
     </row>
     <row r="72">
@@ -1583,16 +1583,16 @@
         <v>45992</v>
       </c>
       <c r="B72">
-        <v>336480.5751487959</v>
+        <v>316873.0485069386</v>
       </c>
       <c r="C72">
-        <v>68871.26739858103</v>
+        <v>71673.75338463462</v>
       </c>
       <c r="D72">
-        <v>9491.369669659336</v>
+        <v>9895.128780829862</v>
       </c>
       <c r="E72">
-        <v>78362.63706824036</v>
+        <v>81568.88216546449</v>
       </c>
     </row>
     <row r="73">
@@ -1600,16 +1600,16 @@
         <v>46023</v>
       </c>
       <c r="B73">
-        <v>332641.9296384334</v>
+        <v>316014.9524377218</v>
       </c>
       <c r="C73">
-        <v>75580.53941807963</v>
+        <v>80759.38116059502</v>
       </c>
       <c r="D73">
-        <v>11407.24291665605</v>
+        <v>11866.98202929734</v>
       </c>
       <c r="E73">
-        <v>86987.78233473568</v>
+        <v>92626.36318989235</v>
       </c>
     </row>
     <row r="74">
@@ -1617,16 +1617,16 @@
         <v>46054</v>
       </c>
       <c r="B74">
-        <v>335168.7343966643</v>
+        <v>320846.9921272756</v>
       </c>
       <c r="C74">
-        <v>69037.78287102637</v>
+        <v>78024.34977450577</v>
       </c>
       <c r="D74">
-        <v>11106.88399703204</v>
+        <v>11691.76009620259</v>
       </c>
       <c r="E74">
-        <v>80144.66686805841</v>
+        <v>89716.10987070836</v>
       </c>
     </row>
     <row r="75">
@@ -1634,16 +1634,16 @@
         <v>46082</v>
       </c>
       <c r="B75">
-        <v>349779.1439455802</v>
+        <v>332643.2851505192</v>
       </c>
       <c r="C75">
-        <v>73145.5076728336</v>
+        <v>81969.33167786912</v>
       </c>
       <c r="D75">
-        <v>15770.05641749954</v>
+        <v>15964.15835400773</v>
       </c>
       <c r="E75">
-        <v>88915.56409033314</v>
+        <v>97933.49003187685</v>
       </c>
     </row>
     <row r="76">
@@ -1651,16 +1651,33 @@
         <v>46113</v>
       </c>
       <c r="B76">
-        <v>364323.152600785</v>
+        <v>345696.4824421374</v>
       </c>
       <c r="C76">
-        <v>72534.53052317322</v>
+        <v>78471.86043474443</v>
       </c>
       <c r="D76">
-        <v>13637.3737597166</v>
+        <v>13763.38854679125</v>
       </c>
       <c r="E76">
-        <v>86171.90428288982</v>
+        <v>92235.24898153568</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B77">
+        <v>365830.6110566787</v>
+      </c>
+      <c r="C77">
+        <v>82797.52461782302</v>
+      </c>
+      <c r="D77">
+        <v>17100.59072851364</v>
+      </c>
+      <c r="E77">
+        <v>99898.11534633665</v>
       </c>
     </row>
   </sheetData>

--- a/output/tablas/numero_plataformas.xlsx
+++ b/output/tablas/numero_plataformas.xlsx
@@ -399,10 +399,10 @@
         <v>48236.60933100921</v>
       </c>
       <c r="D2">
-        <v>7536.406591739306</v>
+        <v>7536.406591739305</v>
       </c>
       <c r="E2">
-        <v>55773.01592274852</v>
+        <v>55773.01592274851</v>
       </c>
     </row>
     <row r="3">
@@ -430,7 +430,7 @@
         <v>47843.97463993884</v>
       </c>
       <c r="C4">
-        <v>30606.92704213435</v>
+        <v>30606.92704213436</v>
       </c>
       <c r="D4">
         <v>3723.824119850708</v>
@@ -444,7 +444,7 @@
         <v>43952</v>
       </c>
       <c r="B5">
-        <v>36777.22027504075</v>
+        <v>36777.22027504076</v>
       </c>
       <c r="C5">
         <v>27117.772757939</v>
@@ -478,7 +478,7 @@
         <v>44013</v>
       </c>
       <c r="B7">
-        <v>98117.57881939619</v>
+        <v>98117.57881939621</v>
       </c>
       <c r="C7">
         <v>32717.66259689889</v>
@@ -495,16 +495,16 @@
         <v>44044</v>
       </c>
       <c r="B8">
-        <v>121003.9877987853</v>
+        <v>121003.9877987854</v>
       </c>
       <c r="C8">
-        <v>31002.4195427435</v>
+        <v>31002.41954274351</v>
       </c>
       <c r="D8">
         <v>4399.545841620967</v>
       </c>
       <c r="E8">
-        <v>35401.96538436447</v>
+        <v>35401.96538436448</v>
       </c>
     </row>
     <row r="9">
@@ -532,13 +532,13 @@
         <v>107611.6822931157</v>
       </c>
       <c r="C10">
-        <v>30302.90515041072</v>
+        <v>30302.90515041073</v>
       </c>
       <c r="D10">
         <v>5568.562666572299</v>
       </c>
       <c r="E10">
-        <v>35871.46781698302</v>
+        <v>35871.46781698303</v>
       </c>
     </row>
     <row r="11">
@@ -569,7 +569,7 @@
         <v>37112.86699439934</v>
       </c>
       <c r="D12">
-        <v>2285.683624272256</v>
+        <v>2285.683624272255</v>
       </c>
       <c r="E12">
         <v>39398.55061867159</v>
@@ -648,7 +648,7 @@
         <v>44317</v>
       </c>
       <c r="B17">
-        <v>143225.3277803313</v>
+        <v>143225.3277803312</v>
       </c>
       <c r="C17">
         <v>48363.63447281568</v>
@@ -668,13 +668,13 @@
         <v>137790.9541693127</v>
       </c>
       <c r="C18">
-        <v>52177.86671649782</v>
+        <v>52177.86671649781</v>
       </c>
       <c r="D18">
         <v>1130.800971739731</v>
       </c>
       <c r="E18">
-        <v>53308.66768823755</v>
+        <v>53308.66768823754</v>
       </c>
     </row>
     <row r="19">
@@ -682,7 +682,7 @@
         <v>44378</v>
       </c>
       <c r="B19">
-        <v>155183.9950436768</v>
+        <v>155183.9950436767</v>
       </c>
       <c r="C19">
         <v>52922.12264192112</v>
@@ -719,7 +719,7 @@
         <v>165045.2938010738</v>
       </c>
       <c r="C21">
-        <v>43461.54117341115</v>
+        <v>43461.54117341114</v>
       </c>
       <c r="D21">
         <v>1958.057217865614</v>
@@ -787,13 +787,13 @@
         <v>169701.0943680634</v>
       </c>
       <c r="C25">
-        <v>59571.37394870307</v>
+        <v>59571.3739487031</v>
       </c>
       <c r="D25">
         <v>8341.293917244337</v>
       </c>
       <c r="E25">
-        <v>67912.66786594741</v>
+        <v>67912.66786594744</v>
       </c>
     </row>
     <row r="26">
@@ -801,7 +801,7 @@
         <v>44593</v>
       </c>
       <c r="B26">
-        <v>166518.3951069183</v>
+        <v>166518.3951069184</v>
       </c>
       <c r="C26">
         <v>58092.493607593</v>
@@ -818,16 +818,16 @@
         <v>44621</v>
       </c>
       <c r="B27">
-        <v>164054.9645784177</v>
+        <v>164054.9645784178</v>
       </c>
       <c r="C27">
-        <v>55694.82736005987</v>
+        <v>55694.82736005986</v>
       </c>
       <c r="D27">
-        <v>6653.598665400261</v>
+        <v>6653.598665400262</v>
       </c>
       <c r="E27">
-        <v>62348.42602546013</v>
+        <v>62348.42602546012</v>
       </c>
     </row>
     <row r="28">
@@ -835,10 +835,10 @@
         <v>44652</v>
       </c>
       <c r="B28">
-        <v>170330.2331582338</v>
+        <v>170330.2331582337</v>
       </c>
       <c r="C28">
-        <v>51841.8393386224</v>
+        <v>51841.83933862239</v>
       </c>
       <c r="D28">
         <v>6196.313964457395</v>
@@ -861,7 +861,7 @@
         <v>6767.273823917919</v>
       </c>
       <c r="E29">
-        <v>55763.64090405427</v>
+        <v>55763.64090405428</v>
       </c>
     </row>
     <row r="30">
@@ -954,16 +954,16 @@
         <v>44866</v>
       </c>
       <c r="B35">
-        <v>181505.8945205147</v>
+        <v>181505.8945205148</v>
       </c>
       <c r="C35">
-        <v>52496.62764393002</v>
+        <v>52496.62764393001</v>
       </c>
       <c r="D35">
         <v>4202.45601309321</v>
       </c>
       <c r="E35">
-        <v>56699.08365702323</v>
+        <v>56699.08365702322</v>
       </c>
     </row>
     <row r="36">
@@ -991,13 +991,13 @@
         <v>188262.5668955287</v>
       </c>
       <c r="C37">
-        <v>51349.00364557674</v>
+        <v>51349.00364557673</v>
       </c>
       <c r="D37">
         <v>4367.302102299227</v>
       </c>
       <c r="E37">
-        <v>55716.30574787597</v>
+        <v>55716.30574787596</v>
       </c>
     </row>
     <row r="38">
@@ -1022,7 +1022,7 @@
         <v>44986</v>
       </c>
       <c r="B39">
-        <v>197811.7489779338</v>
+        <v>197811.7489779339</v>
       </c>
       <c r="C39">
         <v>48776.84671027958</v>
@@ -1056,16 +1056,16 @@
         <v>45047</v>
       </c>
       <c r="B41">
-        <v>214175.7260359662</v>
+        <v>214175.726035966</v>
       </c>
       <c r="C41">
-        <v>56148.85510009451</v>
+        <v>56148.85510009452</v>
       </c>
       <c r="D41">
         <v>5491.023494019693</v>
       </c>
       <c r="E41">
-        <v>61639.8785941142</v>
+        <v>61639.87859411421</v>
       </c>
     </row>
     <row r="42">
@@ -1073,16 +1073,16 @@
         <v>45078</v>
       </c>
       <c r="B42">
-        <v>220672.0385710547</v>
+        <v>220672.0385710546</v>
       </c>
       <c r="C42">
         <v>56175.85054731127</v>
       </c>
       <c r="D42">
-        <v>4563.115995469119</v>
+        <v>4563.115995469118</v>
       </c>
       <c r="E42">
-        <v>60738.96654278038</v>
+        <v>60738.96654278039</v>
       </c>
     </row>
     <row r="43">
@@ -1110,13 +1110,13 @@
         <v>248676.8638880833</v>
       </c>
       <c r="C44">
-        <v>59673.31606542262</v>
+        <v>59673.31606542264</v>
       </c>
       <c r="D44">
-        <v>6739.995184589316</v>
+        <v>6739.995184589317</v>
       </c>
       <c r="E44">
-        <v>66413.31125001193</v>
+        <v>66413.31125001196</v>
       </c>
     </row>
     <row r="45">
@@ -1127,13 +1127,13 @@
         <v>236625.1771884882</v>
       </c>
       <c r="C45">
-        <v>60987.8746948617</v>
+        <v>60987.87469486169</v>
       </c>
       <c r="D45">
         <v>6186.332573723052</v>
       </c>
       <c r="E45">
-        <v>67174.20726858475</v>
+        <v>67174.20726858474</v>
       </c>
     </row>
     <row r="46">
@@ -1141,7 +1141,7 @@
         <v>45200</v>
       </c>
       <c r="B46">
-        <v>233874.361272312</v>
+        <v>233874.3612723119</v>
       </c>
       <c r="C46">
         <v>67559.20649534222</v>
@@ -1161,13 +1161,13 @@
         <v>210444.5394789354</v>
       </c>
       <c r="C47">
-        <v>66357.55189162487</v>
+        <v>66357.5518916249</v>
       </c>
       <c r="D47">
         <v>5309.836827753625</v>
       </c>
       <c r="E47">
-        <v>71667.38871937849</v>
+        <v>71667.38871937852</v>
       </c>
     </row>
     <row r="48">
@@ -1192,7 +1192,7 @@
         <v>45292</v>
       </c>
       <c r="B49">
-        <v>227788.851683885</v>
+        <v>227788.8516838851</v>
       </c>
       <c r="C49">
         <v>62417.07410282281</v>
@@ -1229,13 +1229,13 @@
         <v>241463.6407551908</v>
       </c>
       <c r="C51">
-        <v>74524.31921502581</v>
+        <v>74524.31921502583</v>
       </c>
       <c r="D51">
         <v>10450.5297164524</v>
       </c>
       <c r="E51">
-        <v>84974.84893147821</v>
+        <v>84974.84893147822</v>
       </c>
     </row>
     <row r="52">
@@ -1243,7 +1243,7 @@
         <v>45383</v>
       </c>
       <c r="B52">
-        <v>254035.5851467194</v>
+        <v>254035.5851467193</v>
       </c>
       <c r="C52">
         <v>71891.02901163133</v>
@@ -1280,13 +1280,13 @@
         <v>275677.8393703107</v>
       </c>
       <c r="C54">
-        <v>66687.66343178286</v>
+        <v>66687.66343178287</v>
       </c>
       <c r="D54">
         <v>4993.247923886036</v>
       </c>
       <c r="E54">
-        <v>71680.9113556689</v>
+        <v>71680.91135566891</v>
       </c>
     </row>
     <row r="55">
@@ -1334,7 +1334,7 @@
         <v>75971.56711285215</v>
       </c>
       <c r="D57">
-        <v>5259.718048545041</v>
+        <v>5259.718048545042</v>
       </c>
       <c r="E57">
         <v>81231.28516139719</v>
@@ -1348,13 +1348,13 @@
         <v>279815.0406334464</v>
       </c>
       <c r="C58">
-        <v>73875.54870583532</v>
+        <v>73875.54870583533</v>
       </c>
       <c r="D58">
         <v>4583.35436108143</v>
       </c>
       <c r="E58">
-        <v>78458.90306691674</v>
+        <v>78458.90306691677</v>
       </c>
     </row>
     <row r="59">
@@ -1413,7 +1413,7 @@
         <v>45689</v>
       </c>
       <c r="B62">
-        <v>278515.9339674744</v>
+        <v>278515.9339674743</v>
       </c>
       <c r="C62">
         <v>78734.03363368928</v>
@@ -1487,7 +1487,7 @@
         <v>80728.03281018855</v>
       </c>
       <c r="D66">
-        <v>7474.65359924512</v>
+        <v>7474.653599245119</v>
       </c>
       <c r="E66">
         <v>88202.68640943368</v>
@@ -1498,7 +1498,7 @@
         <v>45839</v>
       </c>
       <c r="B67">
-        <v>332535.4759233722</v>
+        <v>332535.4759233721</v>
       </c>
       <c r="C67">
         <v>81297.1619948232</v>
@@ -1518,13 +1518,13 @@
         <v>335826.1275810536</v>
       </c>
       <c r="C68">
-        <v>80320.8041764456</v>
+        <v>80320.80417644563</v>
       </c>
       <c r="D68">
         <v>7701.962298331651</v>
       </c>
       <c r="E68">
-        <v>88022.76647477725</v>
+        <v>88022.76647477728</v>
       </c>
     </row>
     <row r="69">
@@ -1535,13 +1535,13 @@
         <v>326368.6357175083</v>
       </c>
       <c r="C69">
-        <v>71718.07303737955</v>
+        <v>71718.07303737954</v>
       </c>
       <c r="D69">
         <v>9998.895393984905</v>
       </c>
       <c r="E69">
-        <v>81716.96843136445</v>
+        <v>81716.96843136444</v>
       </c>
     </row>
     <row r="70">
@@ -1549,16 +1549,16 @@
         <v>45931</v>
       </c>
       <c r="B70">
-        <v>312177.1879910644</v>
+        <v>312177.1879910642</v>
       </c>
       <c r="C70">
-        <v>64921.4959795128</v>
+        <v>64921.49597951279</v>
       </c>
       <c r="D70">
-        <v>9776.588288412371</v>
+        <v>9776.588288412373</v>
       </c>
       <c r="E70">
-        <v>74698.08426792518</v>
+        <v>74698.08426792517</v>
       </c>
     </row>
     <row r="71">
@@ -1589,7 +1589,7 @@
         <v>71673.75338463462</v>
       </c>
       <c r="D72">
-        <v>9895.128780829862</v>
+        <v>9895.128780829864</v>
       </c>
       <c r="E72">
         <v>81568.88216546449</v>
@@ -1637,13 +1637,13 @@
         <v>332643.2851505192</v>
       </c>
       <c r="C75">
-        <v>81969.33167786912</v>
+        <v>81969.33167786914</v>
       </c>
       <c r="D75">
         <v>15964.15835400773</v>
       </c>
       <c r="E75">
-        <v>97933.49003187685</v>
+        <v>97933.49003187686</v>
       </c>
     </row>
     <row r="76">
@@ -1657,10 +1657,10 @@
         <v>78471.86043474443</v>
       </c>
       <c r="D76">
-        <v>13763.38854679125</v>
+        <v>13763.38854679126</v>
       </c>
       <c r="E76">
-        <v>92235.24898153568</v>
+        <v>92235.2489815357</v>
       </c>
     </row>
     <row r="77">
@@ -1668,7 +1668,7 @@
         <v>46143</v>
       </c>
       <c r="B77">
-        <v>365830.6110566787</v>
+        <v>365830.6110566788</v>
       </c>
       <c r="C77">
         <v>82797.52461782302</v>
